--- a/6.Banc de tests/bancs-de-test.xlsx
+++ b/6.Banc de tests/bancs-de-test.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louise/Documents/insa/insa4/semestre 2/du capteur au banc de test/Github/MOSH-Insa-Toulouse/2025-2026-4GP-ZoeNonon-LouiseLammertyn/6.Banc de tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C79B1B-E122-B241-9B0D-ED7C4EA925E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5781AC-A938-3A43-B081-422C4F65650A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{ACA903E1-C173-A64A-9CEA-45C788F0B547}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{ACA903E1-C173-A64A-9CEA-45C788F0B547}"/>
   </bookViews>
   <sheets>
     <sheet name="compression" sheetId="1" r:id="rId1"/>
     <sheet name="flexion" sheetId="2" r:id="rId2"/>
+    <sheet name="Flex sensor" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="31">
   <si>
     <t>R0</t>
   </si>
@@ -118,9 +119,6 @@
     <t>pos 36</t>
   </si>
   <si>
-    <t>Resitance</t>
-  </si>
-  <si>
     <t>Tension</t>
   </si>
   <si>
@@ -129,18 +127,30 @@
   <si>
     <t>Test flexion</t>
   </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>resistance</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -181,7 +191,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -381,15 +391,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -400,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -414,14 +415,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -440,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -467,6 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,8 +539,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.2274843519120974"/>
-          <c:y val="4.2819405638811286E-2"/>
+          <c:x val="0.1800468965037568"/>
+          <c:y val="7.1003226702081632E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -3469,6 +3465,651 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Variation de la résistance en fonction de la déformation</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>en flexion</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.24968962959854951"/>
+          <c:y val="4.9220339786768097E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>flex sensor</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:intercept val="0"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Flex sensor'!$D$9:$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.3333333333333334E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.6666666666666671E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7142857142857143E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Flex sensor'!$J$9:$J$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3.2079726578720416</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6351614654869517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5673491551410228</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.8493947040597949</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3966844475676365</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-5298-CA4F-83D0-21B279A9A96D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="927458495"/>
+        <c:axId val="927458047"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="927458495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>ε</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> (Deformation)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927458047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="927458047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                  <a:lnSpc>
+                    <a:spcPct val="100000"/>
+                  </a:lnSpc>
+                  <a:spcBef>
+                    <a:spcPts val="0"/>
+                  </a:spcBef>
+                  <a:spcAft>
+                    <a:spcPts val="0"/>
+                  </a:spcAft>
+                  <a:buClrTx/>
+                  <a:buSzTx/>
+                  <a:buFontTx/>
+                  <a:buNone/>
+                  <a:tabLst/>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                    <a:effectLst/>
+                  </a:rPr>
+                  <a:t>|ΔR|/ R0</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="927458495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -3589,6 +4230,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5137,20 +5818,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>19390</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>778471</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>118661</xdr:rowOff>
+      <xdr:rowOff>60269</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>341122</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>268134</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>152528</xdr:rowOff>
+      <xdr:rowOff>94136</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5251,6 +6448,49 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>320990</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>167473</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>177797</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>157718</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60CA745A-78DC-844C-A661-2E66DD0BF7B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5576,20 +6816,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937BCF46-CDDB-9D43-ADA3-49B6D7768B90}">
-  <dimension ref="A4:W28"/>
+  <dimension ref="A4:S28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="19.33203125" customWidth="1"/>
     <col min="7" max="7" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -5602,31 +6842,28 @@
       <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30" t="s">
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30" t="s">
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
     </row>
-    <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.2</v>
       </c>
@@ -5646,7 +6883,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>0</v>
@@ -5655,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>0</v>
@@ -5664,7 +6901,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>0</v>
@@ -5673,37 +6910,31 @@
         <v>1</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17">
+    <row r="8" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
         <v>0</v>
       </c>
-      <c r="H8" s="19">
+      <c r="H8" s="13">
         <v>388163</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="21"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="21"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="15"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B9" s="9">
         <v>15</v>
       </c>
@@ -5715,13 +6946,13 @@
         <f>A$7/(2*C9)</f>
         <v>1.3333333333333334E-2</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="21" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2">
         <v>388163</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="12">
         <v>308649</v>
       </c>
       <c r="J9" s="3">
@@ -5731,7 +6962,7 @@
       <c r="K9" s="2">
         <v>1674034</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="12">
         <v>1399097</v>
       </c>
       <c r="M9" s="3">
@@ -5741,7 +6972,7 @@
       <c r="N9" s="2">
         <v>2807866</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="12">
         <v>1908847</v>
       </c>
       <c r="P9" s="3">
@@ -5751,18 +6982,15 @@
       <c r="Q9" s="2">
         <v>2645191</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="12">
         <v>2157102</v>
       </c>
       <c r="S9" s="3">
         <f>(R9-Q$9)/Q$9</f>
         <v>-0.18451937875185573</v>
       </c>
-      <c r="U9" s="2"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="3"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B10" s="9">
         <v>20</v>
       </c>
@@ -5774,7 +7002,7 @@
         <f t="shared" ref="D10:D14" si="1">A$7/(2*C10)</f>
         <v>0.01</v>
       </c>
-      <c r="G10" s="28"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="4"/>
       <c r="I10">
         <v>319383</v>
@@ -5807,10 +7035,8 @@
         <f t="shared" ref="S10:S14" si="5">(R10-Q$9)/Q$9</f>
         <v>-0.13815108247381758</v>
       </c>
-      <c r="U10" s="4"/>
-      <c r="W10" s="5"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B11" s="9">
         <v>25</v>
       </c>
@@ -5822,7 +7048,7 @@
         <f t="shared" si="1"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="22"/>
       <c r="H11" s="4"/>
       <c r="I11">
         <v>332474</v>
@@ -5855,10 +7081,8 @@
         <f t="shared" si="5"/>
         <v>-7.0351063495981955E-2</v>
       </c>
-      <c r="U11" s="4"/>
-      <c r="W11" s="5"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B12" s="9">
         <v>30</v>
       </c>
@@ -5870,7 +7094,7 @@
         <f t="shared" si="1"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="G12" s="28"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="4"/>
       <c r="I12">
         <v>334280</v>
@@ -5903,10 +7127,8 @@
         <f t="shared" si="5"/>
         <v>-3.0515376772414542E-2</v>
       </c>
-      <c r="U12" s="4"/>
-      <c r="W12" s="5"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B13" s="9">
         <v>35</v>
       </c>
@@ -5918,7 +7140,7 @@
         <f t="shared" si="1"/>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="G13" s="28"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="4"/>
       <c r="I13">
         <v>338861</v>
@@ -5951,10 +7173,8 @@
         <f t="shared" si="5"/>
         <v>1.0585246963262766E-2</v>
       </c>
-      <c r="U13" s="4"/>
-      <c r="W13" s="5"/>
     </row>
-    <row r="14" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="9">
         <v>40</v>
       </c>
@@ -5966,7 +7186,7 @@
         <f t="shared" si="1"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G14" s="29"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="6"/>
       <c r="I14" s="1">
         <v>345434</v>
@@ -6001,46 +7221,40 @@
         <f t="shared" si="5"/>
         <v>3.4647403533431043E-2</v>
       </c>
-      <c r="U14" s="6"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="7"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H17" s="30" t="s">
+    <row r="17" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30" t="s">
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30" t="s">
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30" t="s">
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
     </row>
-    <row r="18" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="H18" s="10" t="s">
         <v>10</v>
       </c>
@@ -6077,41 +7291,35 @@
       <c r="S18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
     </row>
-    <row r="19" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21">
+    <row r="19" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15">
         <v>0</v>
       </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="21">
+      <c r="K19" s="13"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="15">
         <v>0</v>
       </c>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="21">
+      <c r="Q19" s="13"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="15">
         <v>0</v>
       </c>
-      <c r="U19" s="19"/>
-      <c r="V19" s="20"/>
-      <c r="W19" s="21"/>
     </row>
-    <row r="20" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G20" s="31" t="s">
+    <row r="20" spans="7:19" x14ac:dyDescent="0.2">
+      <c r="G20" s="25" t="s">
         <v>22</v>
       </c>
       <c r="H20" s="2">
         <v>2.14</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="12">
         <v>2.54</v>
       </c>
       <c r="J20" s="3">
@@ -6121,7 +7329,7 @@
       <c r="K20" s="2">
         <v>2.41</v>
       </c>
-      <c r="L20" s="18">
+      <c r="L20" s="12">
         <v>2.86</v>
       </c>
       <c r="M20" s="3">
@@ -6131,7 +7339,7 @@
       <c r="N20" s="2">
         <v>2.5</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="12">
         <v>3.61</v>
       </c>
       <c r="P20" s="3">
@@ -6141,19 +7349,16 @@
       <c r="Q20" s="2">
         <v>2.4300000000000002</v>
       </c>
-      <c r="R20" s="18">
+      <c r="R20" s="12">
         <v>2.95</v>
       </c>
       <c r="S20" s="3">
         <f>(R20-Q$20)/Q$20</f>
         <v>0.2139917695473251</v>
       </c>
-      <c r="U20" s="11"/>
-      <c r="V20" s="12"/>
-      <c r="W20" s="13"/>
     </row>
-    <row r="21" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G21" s="32"/>
+    <row r="21" spans="7:19" x14ac:dyDescent="0.2">
+      <c r="G21" s="26"/>
       <c r="H21" s="4"/>
       <c r="I21">
         <v>2.4700000000000002</v>
@@ -6186,11 +7391,9 @@
         <f t="shared" ref="S21:S25" si="9">(R21-Q$20)/Q$20</f>
         <v>0.15226337448559657</v>
       </c>
-      <c r="U21" s="14"/>
-      <c r="W21" s="13"/>
     </row>
-    <row r="22" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G22" s="32"/>
+    <row r="22" spans="7:19" x14ac:dyDescent="0.2">
+      <c r="G22" s="26"/>
       <c r="H22" s="4"/>
       <c r="I22">
         <v>2.4</v>
@@ -6223,11 +7426,9 @@
         <f t="shared" si="9"/>
         <v>7.4074074074073959E-2</v>
       </c>
-      <c r="U22" s="14"/>
-      <c r="W22" s="13"/>
     </row>
-    <row r="23" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G23" s="32"/>
+    <row r="23" spans="7:19" x14ac:dyDescent="0.2">
+      <c r="G23" s="26"/>
       <c r="H23" s="4"/>
       <c r="I23">
         <v>2.39</v>
@@ -6260,11 +7461,9 @@
         <f t="shared" si="9"/>
         <v>2.8806584362139849E-2</v>
       </c>
-      <c r="U23" s="14"/>
-      <c r="W23" s="13"/>
     </row>
-    <row r="24" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G24" s="32"/>
+    <row r="24" spans="7:19" x14ac:dyDescent="0.2">
+      <c r="G24" s="26"/>
       <c r="H24" s="4"/>
       <c r="I24">
         <v>2.36</v>
@@ -6297,11 +7496,9 @@
         <f t="shared" si="9"/>
         <v>-8.2304526748971252E-3</v>
       </c>
-      <c r="U24" s="14"/>
-      <c r="W24" s="13"/>
     </row>
-    <row r="25" spans="7:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G25" s="33"/>
+    <row r="25" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="27"/>
       <c r="H25" s="6"/>
       <c r="I25" s="1">
         <v>2.34</v>
@@ -6336,16 +7533,13 @@
         <f t="shared" si="9"/>
         <v>-3.2921810699588501E-2</v>
       </c>
-      <c r="U25" s="15"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="13"/>
     </row>
-    <row r="26" spans="7:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="7:19" x14ac:dyDescent="0.2">
       <c r="J26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="7:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="7:19" x14ac:dyDescent="0.2">
       <c r="M27" t="s">
         <v>25</v>
       </c>
@@ -6356,17 +7550,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="7:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="7:19" x14ac:dyDescent="0.2">
       <c r="S28">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="U6:W6"/>
+  <mergeCells count="10">
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="G20:G25"/>
-    <mergeCell ref="U17:W17"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="Q6:S6"/>
@@ -6391,7 +7583,7 @@
   <sheetData>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -6408,26 +7600,26 @@
       <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30" t="s">
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30" t="s">
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="30"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
     </row>
     <row r="7" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -6442,14 +7634,14 @@
       <c r="D7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>28</v>
+      <c r="J7" s="17" t="s">
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>0</v>
@@ -6458,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N7" s="10" t="s">
         <v>0</v>
@@ -6467,7 +7659,7 @@
         <v>1</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>0</v>
@@ -6476,33 +7668,33 @@
         <v>1</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
         <v>0</v>
       </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="26">
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20">
         <v>0</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="21">
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="15">
         <v>0</v>
       </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="21">
+      <c r="N8" s="13"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="15">
         <v>0</v>
       </c>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="21">
+      <c r="Q8" s="13"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="15">
         <v>0</v>
       </c>
     </row>
@@ -6518,11 +7710,11 @@
         <f>A$7/(2*C9)</f>
         <v>1.3333333333333334E-2</v>
       </c>
-      <c r="G9" s="27" t="s">
-        <v>26</v>
+      <c r="G9" s="21" t="s">
+        <v>29</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="18">
+      <c r="I9" s="12">
         <v>860005</v>
       </c>
       <c r="J9" s="3">
@@ -6532,7 +7724,7 @@
       <c r="K9" s="2">
         <v>1933763</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L9" s="12">
         <v>2730484</v>
       </c>
       <c r="M9" s="3">
@@ -6542,7 +7734,7 @@
       <c r="N9" s="2">
         <v>1804292</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="12">
         <v>2881834</v>
       </c>
       <c r="P9" s="3">
@@ -6552,7 +7744,7 @@
       <c r="Q9" s="2">
         <v>4075605</v>
       </c>
-      <c r="R9" s="18">
+      <c r="R9" s="12">
         <v>8253865</v>
       </c>
       <c r="S9" s="3">
@@ -6572,7 +7764,7 @@
         <f t="shared" ref="D10:D14" si="1">A$7/(2*C10)</f>
         <v>0.01</v>
       </c>
-      <c r="G10" s="28"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="4">
         <v>569396</v>
       </c>
@@ -6620,7 +7812,7 @@
         <f t="shared" si="1"/>
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="22"/>
       <c r="H11" s="4"/>
       <c r="I11">
         <v>789790</v>
@@ -6666,7 +7858,7 @@
         <f t="shared" si="1"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="G12" s="28"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="4"/>
       <c r="I12">
         <v>755004</v>
@@ -6712,7 +7904,7 @@
         <f t="shared" si="1"/>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="G13" s="28"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="4"/>
       <c r="I13">
         <v>735395</v>
@@ -6758,7 +7950,7 @@
         <f t="shared" si="1"/>
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G14" s="29"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="6"/>
       <c r="I14" s="1">
         <v>712602</v>
@@ -6803,26 +7995,26 @@
       <c r="D16" s="9"/>
     </row>
     <row r="17" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30" t="s">
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30" t="s">
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30" t="s">
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
     </row>
     <row r="18" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="H18" s="10" t="s">
@@ -6863,35 +8055,35 @@
       </c>
     </row>
     <row r="19" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H19" s="19"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="21">
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15">
         <v>0</v>
       </c>
-      <c r="K19" s="19"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="21">
+      <c r="K19" s="13"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="15">
         <v>0</v>
       </c>
-      <c r="N19" s="19"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="21">
+      <c r="N19" s="13"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="15">
         <v>0</v>
       </c>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="21">
+      <c r="Q19" s="16"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="7:19" x14ac:dyDescent="0.2">
-      <c r="G20" s="27" t="s">
-        <v>27</v>
+      <c r="G20" s="21" t="s">
+        <v>26</v>
       </c>
       <c r="H20" s="2">
         <v>2.41</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="12">
         <v>1.7</v>
       </c>
       <c r="J20" s="3">
@@ -6901,7 +8093,7 @@
       <c r="K20" s="2">
         <v>2.5</v>
       </c>
-      <c r="L20" s="18">
+      <c r="L20" s="12">
         <v>1.73</v>
       </c>
       <c r="M20" s="3">
@@ -6911,7 +8103,7 @@
       <c r="N20" s="2">
         <v>2.4300000000000002</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="12">
         <v>1.56</v>
       </c>
       <c r="P20" s="3">
@@ -6921,7 +8113,7 @@
       <c r="Q20" s="2">
         <v>2.42</v>
       </c>
-      <c r="R20" s="18">
+      <c r="R20" s="12">
         <v>0.7</v>
       </c>
       <c r="S20" s="3">
@@ -6930,7 +8122,7 @@
       </c>
     </row>
     <row r="21" spans="7:19" x14ac:dyDescent="0.2">
-      <c r="G21" s="28"/>
+      <c r="G21" s="22"/>
       <c r="H21" s="4"/>
       <c r="I21">
         <v>1.77</v>
@@ -6965,7 +8157,7 @@
       </c>
     </row>
     <row r="22" spans="7:19" x14ac:dyDescent="0.2">
-      <c r="G22" s="28"/>
+      <c r="G22" s="22"/>
       <c r="H22" s="4"/>
       <c r="I22">
         <v>1.82</v>
@@ -7000,7 +8192,7 @@
       </c>
     </row>
     <row r="23" spans="7:19" x14ac:dyDescent="0.2">
-      <c r="G23" s="28"/>
+      <c r="G23" s="22"/>
       <c r="H23" s="4"/>
       <c r="I23">
         <v>1.9</v>
@@ -7035,7 +8227,7 @@
       </c>
     </row>
     <row r="24" spans="7:19" x14ac:dyDescent="0.2">
-      <c r="G24" s="28"/>
+      <c r="G24" s="22"/>
       <c r="H24" s="4"/>
       <c r="I24">
         <v>1.94</v>
@@ -7070,7 +8262,7 @@
       </c>
     </row>
     <row r="25" spans="7:19" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="G25" s="29"/>
+      <c r="G25" s="23"/>
       <c r="H25" s="6"/>
       <c r="I25" s="1">
         <v>1.99</v>
@@ -7141,4 +8333,320 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE4981E-6AE3-9844-BDDD-B597AF7B4B14}">
+  <dimension ref="A4:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+    </row>
+    <row r="7" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.2</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>31307</v>
+      </c>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="9">
+        <v>15</v>
+      </c>
+      <c r="C9" s="9">
+        <f>B9/2</f>
+        <v>7.5</v>
+      </c>
+      <c r="D9" s="9">
+        <f>A$7/(2*C9)</f>
+        <v>1.3333333333333334E-2</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2">
+        <v>31307</v>
+      </c>
+      <c r="I9" s="12">
+        <v>131739</v>
+      </c>
+      <c r="J9" s="3">
+        <f>(I9-H$8)/H$8</f>
+        <v>3.2079726578720416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="9">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9">
+        <f t="shared" ref="C10:C14" si="0">B10/2</f>
+        <v>10</v>
+      </c>
+      <c r="D10" s="9">
+        <f t="shared" ref="D10:D14" si="1">A$7/(2*C10)</f>
+        <v>0.01</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="28">
+        <v>113806</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" ref="J10:J13" si="2">(I10-H$8)/H$8</f>
+        <v>2.6351614654869517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B11" s="9">
+        <v>25</v>
+      </c>
+      <c r="C11" s="9">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="D11" s="9">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="28">
+        <v>111683</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.5673491551410228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="9">
+        <v>30</v>
+      </c>
+      <c r="C12" s="9">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D12" s="9">
+        <f t="shared" si="1"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="4"/>
+      <c r="I12">
+        <v>89206</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8493947040597949</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="9">
+        <v>35</v>
+      </c>
+      <c r="C13" s="9">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="D13" s="9">
+        <f t="shared" si="1"/>
+        <v>5.7142857142857143E-3</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="4"/>
+      <c r="I13">
+        <v>75033</v>
+      </c>
+      <c r="J13" s="3">
+        <f t="shared" si="2"/>
+        <v>1.3966844475676365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="9">
+        <v>40</v>
+      </c>
+      <c r="C14" s="9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="D14" s="9">
+        <f t="shared" si="1"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G14" s="23"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="7:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H17" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+    </row>
+    <row r="18" spans="7:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G20" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3</v>
+      </c>
+      <c r="I20" s="12">
+        <v>1.31</v>
+      </c>
+      <c r="J20" s="3">
+        <f>ABS(I20-H$20)/H$20</f>
+        <v>0.56333333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G21" s="26"/>
+      <c r="H21" s="4"/>
+      <c r="I21">
+        <v>1.46</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" ref="J21:J25" si="3">ABS(I21-H$20)/H$20</f>
+        <v>0.51333333333333331</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G22" s="26"/>
+      <c r="H22" s="4"/>
+      <c r="I22">
+        <v>1.48</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="3"/>
+        <v>0.50666666666666671</v>
+      </c>
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G23" s="26"/>
+      <c r="H23" s="4"/>
+      <c r="I23">
+        <v>1.72</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="3"/>
+        <v>0.42666666666666669</v>
+      </c>
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="G24" s="26"/>
+      <c r="H24" s="4"/>
+      <c r="I24">
+        <v>1.93</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" si="3"/>
+        <v>0.35666666666666669</v>
+      </c>
+    </row>
+    <row r="25" spans="7:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="27"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="7"/>
+    </row>
+    <row r="26" spans="7:10" x14ac:dyDescent="0.2">
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="G20:G25"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="G9:G14"/>
+    <mergeCell ref="H17:J17"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>